--- a/Result/profitability/3402.xlsx
+++ b/Result/profitability/3402.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.64875</v>
+        <v>1.68875</v>
       </c>
       <c r="N2" t="n">
-        <v>21.99375</v>
+        <v>21.8425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6275</v>
+        <v>1.65875</v>
       </c>
       <c r="N3" t="n">
-        <v>20.34125</v>
+        <v>19.865</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.55125</v>
+        <v>1.595</v>
       </c>
       <c r="N4" t="n">
-        <v>19.0725</v>
+        <v>18.83875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9550000000000001</v>
+        <v>0.93625</v>
       </c>
       <c r="N5" t="n">
-        <v>18.405</v>
+        <v>17.51625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7625</v>
+        <v>0.76875</v>
       </c>
       <c r="N6" t="n">
-        <v>18.17875</v>
+        <v>17.75375</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5637500000000001</v>
+        <v>0.635</v>
       </c>
       <c r="N7" t="n">
-        <v>17.1525</v>
+        <v>17.22125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.42875</v>
+        <v>0.49375</v>
       </c>
       <c r="N8" t="n">
-        <v>18.50625</v>
+        <v>18.51875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1571</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E75" t="n">
+        <v>332</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>189</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>196</v>
+      </c>
+      <c r="K75" t="n">
+        <v>152</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.84125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.19375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.004761904761904745</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.06726457399103136</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2520382842963488</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
